--- a/data/standard_sentences_v2.xlsx
+++ b/data/standard_sentences_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://qubstudentcloud-my.sharepoint.com/personal/40455223_ads_qub_ac_uk/Documents/idioms/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D1AA09D4-675D-A144-9EB1-72D989EA64F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68070611-B619-415F-BA52-4C9790E5ED72}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{27E8A9B7-4BC5-2F41-81BD-061728839778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A85CF00-3966-49E7-BFD6-F313297E71F9}"/>
   <bookViews>
     <workbookView xWindow="34800" yWindow="1515" windowWidth="20805" windowHeight="13770" xr2:uid="{63D38C62-83DD-5040-917F-144BFF8A8431}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="676">
   <si>
     <t>idiom</t>
   </si>
@@ -458,9 +458,6 @@
     <t>the determined man turned the tables and</t>
   </si>
   <si>
-    <t>the young man cleaned the tables and</t>
-  </si>
-  <si>
     <t>cleaned</t>
   </si>
   <si>
@@ -593,24 +590,12 @@
     <t>the brave man took the plunge and</t>
   </si>
   <si>
-    <t>the young man took the book and</t>
-  </si>
-  <si>
     <t>book</t>
   </si>
   <si>
-    <t>the brave man took the book and</t>
-  </si>
-  <si>
-    <t>the young man survived a plunge and</t>
-  </si>
-  <si>
     <t>survived</t>
   </si>
   <si>
-    <t>the brave man survived a plunge and</t>
-  </si>
-  <si>
     <t>the young man committed to something risky and</t>
   </si>
   <si>
@@ -1283,9 +1268,6 @@
     <t>determined</t>
   </si>
   <si>
-    <t>the determined man cleaned the tables and</t>
-  </si>
-  <si>
     <t>the determined man reversed the situation and</t>
   </si>
   <si>
@@ -2052,6 +2034,30 @@
   </si>
   <si>
     <t>the lazy man wouldn’t move a hand and</t>
+  </si>
+  <si>
+    <t>the young man cleaned the surfaces and</t>
+  </si>
+  <si>
+    <t>the determined man cleaned the surfaces and</t>
+  </si>
+  <si>
+    <t>surfaces</t>
+  </si>
+  <si>
+    <t>the young man grabbed the book and</t>
+  </si>
+  <si>
+    <t>the brave man grabbed the book and</t>
+  </si>
+  <si>
+    <t>the young man survived a dive and</t>
+  </si>
+  <si>
+    <t>the brave man survived a dive and</t>
+  </si>
+  <si>
+    <t>dive</t>
   </si>
   <si>
     <t>the young man started the society and</t>
@@ -2451,19 +2457,19 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="H1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="I1" t="s">
         <v>3</v>
@@ -2489,10 +2495,10 @@
         <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -2512,10 +2518,10 @@
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I3" t="s">
         <v>8</v>
@@ -2523,10 +2529,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D4" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -2535,10 +2541,10 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H4" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
@@ -2546,10 +2552,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D5" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -2558,10 +2564,10 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H5" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I5" t="s">
         <v>11</v>
@@ -2569,22 +2575,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F6" t="s">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H6" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I6" t="s">
         <v>11</v>
@@ -2592,22 +2598,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F7" t="s">
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H7" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I7" t="s">
         <v>11</v>
@@ -2627,10 +2633,10 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H8" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I8" t="s">
         <v>11</v>
@@ -2650,10 +2656,10 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H9" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I9" t="s">
         <v>11</v>
@@ -2679,10 +2685,10 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H10" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I10" t="s">
         <v>8</v>
@@ -2702,10 +2708,10 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H11" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I11" t="s">
         <v>8</v>
@@ -2713,10 +2719,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D12" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E12" t="s">
         <v>22</v>
@@ -2725,10 +2731,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H12" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I12" t="s">
         <v>11</v>
@@ -2736,10 +2742,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D13" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
@@ -2748,10 +2754,10 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H13" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I13" t="s">
         <v>11</v>
@@ -2759,22 +2765,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="F14" t="s">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H14" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I14" t="s">
         <v>11</v>
@@ -2782,22 +2788,22 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="F15" t="s">
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H15" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I15" t="s">
         <v>11</v>
@@ -2805,22 +2811,22 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D16" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E16" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="F16" t="s">
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H16" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I16" t="s">
         <v>11</v>
@@ -2828,22 +2834,22 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D17" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E17" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="F17" t="s">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H17" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I17" t="s">
         <v>11</v>
@@ -2869,10 +2875,10 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H18" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="I18" t="s">
         <v>8</v>
@@ -2892,10 +2898,10 @@
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H19" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="I19" t="s">
         <v>8</v>
@@ -2903,10 +2909,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D20" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
@@ -2915,10 +2921,10 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H20" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I20" t="s">
         <v>11</v>
@@ -2926,10 +2932,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D21" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
@@ -2938,10 +2944,10 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H21" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I21" t="s">
         <v>11</v>
@@ -2949,22 +2955,22 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D22" t="s">
         <v>30</v>
       </c>
       <c r="E22" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="F22" t="s">
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H22" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I22" t="s">
         <v>11</v>
@@ -2972,22 +2978,22 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D23" t="s">
         <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="F23" t="s">
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H23" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I23" t="s">
         <v>11</v>
@@ -3007,10 +3013,10 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H24" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I24" t="s">
         <v>11</v>
@@ -3018,7 +3024,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
@@ -3030,10 +3036,10 @@
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H25" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I25" t="s">
         <v>11</v>
@@ -3059,10 +3065,10 @@
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H26" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I26" t="s">
         <v>8</v>
@@ -3082,10 +3088,10 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H27" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I27" t="s">
         <v>8</v>
@@ -3093,10 +3099,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="D28" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E28" t="s">
         <v>39</v>
@@ -3105,10 +3111,10 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H28" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I28" t="s">
         <v>11</v>
@@ -3116,10 +3122,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="D29" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="E29" t="s">
         <v>39</v>
@@ -3128,10 +3134,10 @@
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H29" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I29" t="s">
         <v>11</v>
@@ -3139,22 +3145,22 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="D30" t="s">
         <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="F30" t="s">
         <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H30" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I30" t="s">
         <v>11</v>
@@ -3162,22 +3168,22 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D31" t="s">
         <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="F31" t="s">
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H31" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I31" t="s">
         <v>11</v>
@@ -3197,10 +3203,10 @@
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H32" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I32" t="s">
         <v>11</v>
@@ -3220,10 +3226,10 @@
         <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H33" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I33" t="s">
         <v>11</v>
@@ -3249,10 +3255,10 @@
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H34" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I34" t="s">
         <v>8</v>
@@ -3272,10 +3278,10 @@
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H35" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I35" t="s">
         <v>8</v>
@@ -3283,10 +3289,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D36" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E36" t="s">
         <v>50</v>
@@ -3295,10 +3301,10 @@
         <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H36" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I36" t="s">
         <v>11</v>
@@ -3306,10 +3312,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D37" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E37" t="s">
         <v>50</v>
@@ -3318,10 +3324,10 @@
         <v>2</v>
       </c>
       <c r="G37" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H37" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I37" t="s">
         <v>11</v>
@@ -3329,22 +3335,22 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D38" t="s">
         <v>51</v>
       </c>
       <c r="E38" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F38" t="s">
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H38" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I38" t="s">
         <v>11</v>
@@ -3352,22 +3358,22 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D39" t="s">
         <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F39" t="s">
         <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H39" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I39" t="s">
         <v>11</v>
@@ -3375,22 +3381,22 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="D40" t="s">
         <v>52</v>
       </c>
       <c r="E40" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="F40" t="s">
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H40" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I40" t="s">
         <v>11</v>
@@ -3398,22 +3404,22 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D41" t="s">
         <v>52</v>
       </c>
       <c r="E41" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="F41" t="s">
         <v>2</v>
       </c>
       <c r="G41" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H41" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I41" t="s">
         <v>11</v>
@@ -3439,10 +3445,10 @@
         <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H42" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I42" t="s">
         <v>8</v>
@@ -3462,10 +3468,10 @@
         <v>2</v>
       </c>
       <c r="G43" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="H43" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I43" t="s">
         <v>8</v>
@@ -3473,7 +3479,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="D44" t="s">
         <v>95</v>
@@ -3485,10 +3491,10 @@
         <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H44" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I44" t="s">
         <v>11</v>
@@ -3496,7 +3502,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="D45" t="s">
         <v>95</v>
@@ -3508,10 +3514,10 @@
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="H45" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I45" t="s">
         <v>11</v>
@@ -3519,22 +3525,22 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D46" t="s">
         <v>60</v>
       </c>
       <c r="E46" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F46" t="s">
         <v>2</v>
       </c>
       <c r="G46" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H46" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I46" t="s">
         <v>11</v>
@@ -3542,22 +3548,22 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D47" t="s">
         <v>60</v>
       </c>
       <c r="E47" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F47" t="s">
         <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="H47" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I47" t="s">
         <v>11</v>
@@ -3577,10 +3583,10 @@
         <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H48" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I48" t="s">
         <v>11</v>
@@ -3600,10 +3606,10 @@
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="H49" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I49" t="s">
         <v>11</v>
@@ -3629,10 +3635,10 @@
         <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H50" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I50" t="s">
         <v>8</v>
@@ -3652,10 +3658,10 @@
         <v>2</v>
       </c>
       <c r="G51" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H51" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I51" t="s">
         <v>8</v>
@@ -3663,7 +3669,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="D52" t="s">
         <v>60</v>
@@ -3675,10 +3681,10 @@
         <v>2</v>
       </c>
       <c r="G52" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H52" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I52" t="s">
         <v>11</v>
@@ -3686,7 +3692,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C53" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D53" t="s">
         <v>60</v>
@@ -3698,10 +3704,10 @@
         <v>2</v>
       </c>
       <c r="G53" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H53" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I53" t="s">
         <v>11</v>
@@ -3709,22 +3715,22 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="D54" t="s">
         <v>71</v>
       </c>
       <c r="E54" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F54" t="s">
         <v>2</v>
       </c>
       <c r="G54" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H54" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I54" t="s">
         <v>11</v>
@@ -3732,22 +3738,22 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C55" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D55" t="s">
         <v>71</v>
       </c>
       <c r="E55" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F55" t="s">
         <v>2</v>
       </c>
       <c r="G55" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H55" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I55" t="s">
         <v>11</v>
@@ -3767,10 +3773,10 @@
         <v>2</v>
       </c>
       <c r="G56" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H56" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I56" t="s">
         <v>11</v>
@@ -3790,10 +3796,10 @@
         <v>2</v>
       </c>
       <c r="G57" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H57" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I57" t="s">
         <v>11</v>
@@ -3807,10 +3813,10 @@
         <v>76</v>
       </c>
       <c r="C58" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D58" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E58" t="s">
         <v>77</v>
@@ -3819,10 +3825,10 @@
         <v>2</v>
       </c>
       <c r="G58" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H58" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I58" t="s">
         <v>8</v>
@@ -3830,10 +3836,10 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D59" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E59" t="s">
         <v>77</v>
@@ -3842,10 +3848,10 @@
         <v>2</v>
       </c>
       <c r="G59" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H59" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I59" t="s">
         <v>8</v>
@@ -3853,10 +3859,10 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="D60" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E60" t="s">
         <v>78</v>
@@ -3865,10 +3871,10 @@
         <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H60" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I60" t="s">
         <v>11</v>
@@ -3876,10 +3882,10 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C61" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D61" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E61" t="s">
         <v>78</v>
@@ -3888,10 +3894,10 @@
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H61" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I61" t="s">
         <v>11</v>
@@ -3899,22 +3905,22 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="D62" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E62" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="F62" t="s">
         <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H62" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I62" t="s">
         <v>11</v>
@@ -3922,22 +3928,22 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C63" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D63" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E63" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="F63" t="s">
         <v>2</v>
       </c>
       <c r="G63" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H63" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I63" t="s">
         <v>11</v>
@@ -3945,10 +3951,10 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D64" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E64" t="s">
         <v>79</v>
@@ -3957,10 +3963,10 @@
         <v>2</v>
       </c>
       <c r="G64" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H64" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I64" t="s">
         <v>11</v>
@@ -3968,10 +3974,10 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C65" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D65" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E65" t="s">
         <v>79</v>
@@ -3980,10 +3986,10 @@
         <v>2</v>
       </c>
       <c r="G65" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H65" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I65" t="s">
         <v>11</v>
@@ -4009,10 +4015,10 @@
         <v>2</v>
       </c>
       <c r="G66" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H66" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I66" t="s">
         <v>8</v>
@@ -4032,10 +4038,10 @@
         <v>2</v>
       </c>
       <c r="G67" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H67" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I67" t="s">
         <v>8</v>
@@ -4043,10 +4049,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D68" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E68" t="s">
         <v>85</v>
@@ -4055,10 +4061,10 @@
         <v>2</v>
       </c>
       <c r="G68" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H68" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I68" t="s">
         <v>11</v>
@@ -4066,10 +4072,10 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C69" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="D69" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E69" t="s">
         <v>85</v>
@@ -4078,10 +4084,10 @@
         <v>2</v>
       </c>
       <c r="G69" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H69" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I69" t="s">
         <v>11</v>
@@ -4089,22 +4095,22 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D70" t="s">
         <v>105</v>
       </c>
       <c r="E70" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="F70" t="s">
         <v>2</v>
       </c>
       <c r="G70" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H70" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I70" t="s">
         <v>11</v>
@@ -4112,22 +4118,22 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C71" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D71" t="s">
         <v>105</v>
       </c>
       <c r="E71" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="F71" t="s">
         <v>2</v>
       </c>
       <c r="G71" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H71" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I71" t="s">
         <v>11</v>
@@ -4147,10 +4153,10 @@
         <v>2</v>
       </c>
       <c r="G72" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H72" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I72" t="s">
         <v>11</v>
@@ -4170,10 +4176,10 @@
         <v>2</v>
       </c>
       <c r="G73" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H73" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I73" t="s">
         <v>11</v>
@@ -4199,10 +4205,10 @@
         <v>2</v>
       </c>
       <c r="G74" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H74" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I74" t="s">
         <v>8</v>
@@ -4222,10 +4228,10 @@
         <v>2</v>
       </c>
       <c r="G75" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H75" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I75" t="s">
         <v>8</v>
@@ -4233,7 +4239,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="D76" t="s">
         <v>101</v>
@@ -4245,10 +4251,10 @@
         <v>2</v>
       </c>
       <c r="G76" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H76" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I76" t="s">
         <v>11</v>
@@ -4256,7 +4262,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C77" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="D77" t="s">
         <v>101</v>
@@ -4268,10 +4274,10 @@
         <v>2</v>
       </c>
       <c r="G77" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H77" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I77" t="s">
         <v>11</v>
@@ -4279,22 +4285,22 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C78" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D78" t="s">
         <v>95</v>
       </c>
       <c r="E78" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="F78" t="s">
         <v>2</v>
       </c>
       <c r="G78" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H78" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I78" t="s">
         <v>11</v>
@@ -4302,22 +4308,22 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C79" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D79" t="s">
         <v>95</v>
       </c>
       <c r="E79" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="F79" t="s">
         <v>2</v>
       </c>
       <c r="G79" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H79" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I79" t="s">
         <v>11</v>
@@ -4337,10 +4343,10 @@
         <v>2</v>
       </c>
       <c r="G80" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H80" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I80" t="s">
         <v>11</v>
@@ -4360,10 +4366,10 @@
         <v>2</v>
       </c>
       <c r="G81" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H81" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I81" t="s">
         <v>11</v>
@@ -4389,10 +4395,10 @@
         <v>2</v>
       </c>
       <c r="G82" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H82" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I82" t="s">
         <v>8</v>
@@ -4412,10 +4418,10 @@
         <v>2</v>
       </c>
       <c r="G83" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H83" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I83" t="s">
         <v>8</v>
@@ -4423,10 +4429,10 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C84" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="D84" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="E84" t="s">
         <v>104</v>
@@ -4435,10 +4441,10 @@
         <v>2</v>
       </c>
       <c r="G84" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H84" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I84" t="s">
         <v>11</v>
@@ -4446,10 +4452,10 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C85" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D85" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="E85" t="s">
         <v>104</v>
@@ -4458,10 +4464,10 @@
         <v>2</v>
       </c>
       <c r="G85" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H85" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I85" t="s">
         <v>11</v>
@@ -4469,22 +4475,22 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="D86" t="s">
         <v>105</v>
       </c>
       <c r="E86" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F86" t="s">
         <v>2</v>
       </c>
       <c r="G86" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H86" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I86" t="s">
         <v>11</v>
@@ -4492,22 +4498,22 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D87" t="s">
         <v>105</v>
       </c>
       <c r="E87" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F87" t="s">
         <v>2</v>
       </c>
       <c r="G87" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H87" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I87" t="s">
         <v>11</v>
@@ -4527,10 +4533,10 @@
         <v>2</v>
       </c>
       <c r="G88" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H88" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I88" t="s">
         <v>11</v>
@@ -4550,10 +4556,10 @@
         <v>2</v>
       </c>
       <c r="G89" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H89" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I89" t="s">
         <v>11</v>
@@ -4579,10 +4585,10 @@
         <v>2</v>
       </c>
       <c r="G90" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H90" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I90" t="s">
         <v>8</v>
@@ -4602,10 +4608,10 @@
         <v>2</v>
       </c>
       <c r="G91" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H91" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I91" t="s">
         <v>8</v>
@@ -4613,22 +4619,22 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C92" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D92" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E92" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F92" t="s">
         <v>2</v>
       </c>
       <c r="G92" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H92" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I92" t="s">
         <v>11</v>
@@ -4636,22 +4642,22 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C93" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D93" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E93" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F93" t="s">
         <v>2</v>
       </c>
       <c r="G93" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H93" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I93" t="s">
         <v>11</v>
@@ -4659,22 +4665,22 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C94" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D94" t="s">
         <v>114</v>
       </c>
       <c r="E94" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="F94" t="s">
         <v>2</v>
       </c>
       <c r="G94" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H94" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I94" t="s">
         <v>11</v>
@@ -4682,22 +4688,22 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="D95" t="s">
         <v>114</v>
       </c>
       <c r="E95" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="F95" t="s">
         <v>2</v>
       </c>
       <c r="G95" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H95" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I95" t="s">
         <v>11</v>
@@ -4705,22 +4711,22 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C96" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D96" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E96" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F96" t="s">
         <v>2</v>
       </c>
       <c r="G96" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H96" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I96" t="s">
         <v>11</v>
@@ -4728,22 +4734,22 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C97" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D97" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E97" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F97" t="s">
         <v>2</v>
       </c>
       <c r="G97" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H97" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I97" t="s">
         <v>11</v>
@@ -4769,10 +4775,10 @@
         <v>2</v>
       </c>
       <c r="G98" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H98" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I98" t="s">
         <v>8</v>
@@ -4792,10 +4798,10 @@
         <v>2</v>
       </c>
       <c r="G99" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H99" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I99" t="s">
         <v>8</v>
@@ -4803,10 +4809,10 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C100" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D100" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="E100" t="s">
         <v>120</v>
@@ -4815,10 +4821,10 @@
         <v>2</v>
       </c>
       <c r="G100" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H100" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I100" t="s">
         <v>11</v>
@@ -4826,10 +4832,10 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C101" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="D101" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="E101" t="s">
         <v>120</v>
@@ -4838,10 +4844,10 @@
         <v>2</v>
       </c>
       <c r="G101" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H101" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I101" t="s">
         <v>11</v>
@@ -4849,22 +4855,22 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C102" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D102" t="s">
         <v>121</v>
       </c>
       <c r="E102" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="F102" t="s">
         <v>2</v>
       </c>
       <c r="G102" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H102" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I102" t="s">
         <v>11</v>
@@ -4872,22 +4878,22 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C103" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="D103" t="s">
         <v>121</v>
       </c>
       <c r="E103" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="F103" t="s">
         <v>2</v>
       </c>
       <c r="G103" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H103" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I103" t="s">
         <v>11</v>
@@ -4907,10 +4913,10 @@
         <v>2</v>
       </c>
       <c r="G104" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H104" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I104" t="s">
         <v>11</v>
@@ -4930,10 +4936,10 @@
         <v>2</v>
       </c>
       <c r="G105" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H105" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I105" t="s">
         <v>11</v>
@@ -4959,10 +4965,10 @@
         <v>2</v>
       </c>
       <c r="G106" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H106" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I106" t="s">
         <v>8</v>
@@ -4982,10 +4988,10 @@
         <v>2</v>
       </c>
       <c r="G107" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H107" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I107" t="s">
         <v>8</v>
@@ -4993,10 +4999,10 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C108" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D108" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="E108" t="s">
         <v>130</v>
@@ -5005,10 +5011,10 @@
         <v>2</v>
       </c>
       <c r="G108" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H108" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I108" t="s">
         <v>11</v>
@@ -5016,10 +5022,10 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C109" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D109" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="E109" t="s">
         <v>130</v>
@@ -5028,10 +5034,10 @@
         <v>2</v>
       </c>
       <c r="G109" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H109" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I109" t="s">
         <v>11</v>
@@ -5039,22 +5045,22 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C110" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="D110" t="s">
         <v>131</v>
       </c>
       <c r="E110" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="F110" t="s">
         <v>2</v>
       </c>
       <c r="G110" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H110" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I110" t="s">
         <v>11</v>
@@ -5062,22 +5068,22 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C111" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D111" t="s">
         <v>131</v>
       </c>
       <c r="E111" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="F111" t="s">
         <v>2</v>
       </c>
       <c r="G111" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H111" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I111" t="s">
         <v>11</v>
@@ -5097,10 +5103,10 @@
         <v>2</v>
       </c>
       <c r="G112" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H112" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I112" t="s">
         <v>11</v>
@@ -5120,10 +5126,10 @@
         <v>2</v>
       </c>
       <c r="G113" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H113" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I113" t="s">
         <v>11</v>
@@ -5149,10 +5155,10 @@
         <v>2</v>
       </c>
       <c r="G114" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H114" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I114" t="s">
         <v>8</v>
@@ -5172,10 +5178,10 @@
         <v>2</v>
       </c>
       <c r="G115" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H115" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I115" t="s">
         <v>8</v>
@@ -5183,22 +5189,22 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C116" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="D116" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E116" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F116" t="s">
         <v>2</v>
       </c>
       <c r="G116" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H116" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I116" t="s">
         <v>11</v>
@@ -5206,22 +5212,22 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C117" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D117" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E117" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F117" t="s">
         <v>2</v>
       </c>
       <c r="G117" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H117" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I117" t="s">
         <v>11</v>
@@ -5229,22 +5235,22 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C118" t="s">
+        <v>666</v>
+      </c>
+      <c r="D118" t="s">
         <v>140</v>
       </c>
-      <c r="D118" t="s">
-        <v>141</v>
-      </c>
       <c r="E118" t="s">
-        <v>138</v>
+        <v>668</v>
       </c>
       <c r="F118" t="s">
         <v>2</v>
       </c>
       <c r="G118" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H118" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I118" t="s">
         <v>11</v>
@@ -5252,22 +5258,22 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C119" t="s">
-        <v>415</v>
+        <v>667</v>
       </c>
       <c r="D119" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E119" t="s">
-        <v>138</v>
+        <v>668</v>
       </c>
       <c r="F119" t="s">
         <v>2</v>
       </c>
       <c r="G119" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H119" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I119" t="s">
         <v>11</v>
@@ -5275,22 +5281,22 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C120" t="s">
+        <v>141</v>
+      </c>
+      <c r="D120" t="s">
         <v>142</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>143</v>
       </c>
-      <c r="E120" t="s">
-        <v>144</v>
-      </c>
       <c r="F120" t="s">
         <v>2</v>
       </c>
       <c r="G120" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H120" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I120" t="s">
         <v>11</v>
@@ -5298,22 +5304,22 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C121" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D121" t="s">
+        <v>142</v>
+      </c>
+      <c r="E121" t="s">
         <v>143</v>
       </c>
-      <c r="E121" t="s">
-        <v>144</v>
-      </c>
       <c r="F121" t="s">
         <v>2</v>
       </c>
       <c r="G121" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H121" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I121" t="s">
         <v>11</v>
@@ -5324,25 +5330,25 @@
         <v>16</v>
       </c>
       <c r="B122" t="s">
+        <v>144</v>
+      </c>
+      <c r="C122" t="s">
         <v>145</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>146</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>147</v>
       </c>
-      <c r="E122" t="s">
-        <v>148</v>
-      </c>
       <c r="F122" t="s">
         <v>2</v>
       </c>
       <c r="G122" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H122" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I122" t="s">
         <v>8</v>
@@ -5350,22 +5356,22 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C123" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D123" t="s">
+        <v>146</v>
+      </c>
+      <c r="E123" t="s">
         <v>147</v>
       </c>
-      <c r="E123" t="s">
-        <v>148</v>
-      </c>
       <c r="F123" t="s">
         <v>2</v>
       </c>
       <c r="G123" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="H123" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I123" t="s">
         <v>8</v>
@@ -5373,22 +5379,22 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C124" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D124" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="E124" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F124" t="s">
         <v>2</v>
       </c>
       <c r="G124" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H124" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I124" t="s">
         <v>11</v>
@@ -5396,22 +5402,22 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C125" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="D125" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="E125" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F125" t="s">
         <v>2</v>
       </c>
       <c r="G125" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="H125" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I125" t="s">
         <v>11</v>
@@ -5419,22 +5425,22 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C126" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="D126" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E126" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="F126" t="s">
         <v>2</v>
       </c>
       <c r="G126" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H126" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I126" t="s">
         <v>11</v>
@@ -5442,22 +5448,22 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C127" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D127" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E127" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="F127" t="s">
         <v>2</v>
       </c>
       <c r="G127" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="H127" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I127" t="s">
         <v>11</v>
@@ -5465,22 +5471,22 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C128" t="s">
+        <v>151</v>
+      </c>
+      <c r="D128" t="s">
         <v>152</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>153</v>
       </c>
-      <c r="E128" t="s">
-        <v>154</v>
-      </c>
       <c r="F128" t="s">
         <v>2</v>
       </c>
       <c r="G128" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H128" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I128" t="s">
         <v>11</v>
@@ -5488,22 +5494,22 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C129" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D129" t="s">
+        <v>152</v>
+      </c>
+      <c r="E129" t="s">
         <v>153</v>
       </c>
-      <c r="E129" t="s">
-        <v>154</v>
-      </c>
       <c r="F129" t="s">
         <v>2</v>
       </c>
       <c r="G129" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="H129" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I129" t="s">
         <v>11</v>
@@ -5514,25 +5520,25 @@
         <v>17</v>
       </c>
       <c r="B130" t="s">
+        <v>155</v>
+      </c>
+      <c r="C130" t="s">
         <v>156</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
         <v>157</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
         <v>158</v>
       </c>
-      <c r="E130" t="s">
-        <v>159</v>
-      </c>
       <c r="F130" t="s">
         <v>2</v>
       </c>
       <c r="G130" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H130" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I130" t="s">
         <v>8</v>
@@ -5540,22 +5546,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C131" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D131" t="s">
+        <v>157</v>
+      </c>
+      <c r="E131" t="s">
         <v>158</v>
       </c>
-      <c r="E131" t="s">
-        <v>159</v>
-      </c>
       <c r="F131" t="s">
         <v>2</v>
       </c>
       <c r="G131" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="H131" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I131" t="s">
         <v>8</v>
@@ -5563,22 +5569,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C132" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D132" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E132" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F132" t="s">
         <v>2</v>
       </c>
       <c r="G132" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H132" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I132" t="s">
         <v>11</v>
@@ -5586,22 +5592,22 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C133" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D133" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E133" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F133" t="s">
         <v>2</v>
       </c>
       <c r="G133" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="H133" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I133" t="s">
         <v>11</v>
@@ -5609,22 +5615,22 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C134" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="D134" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E134" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="F134" t="s">
         <v>2</v>
       </c>
       <c r="G134" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H134" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I134" t="s">
         <v>11</v>
@@ -5632,22 +5638,22 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C135" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="D135" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E135" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="F135" t="s">
         <v>2</v>
       </c>
       <c r="G135" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="H135" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I135" t="s">
         <v>11</v>
@@ -5655,22 +5661,22 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C136" t="s">
+        <v>161</v>
+      </c>
+      <c r="D136" t="s">
         <v>162</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
         <v>163</v>
       </c>
-      <c r="E136" t="s">
-        <v>164</v>
-      </c>
       <c r="F136" t="s">
         <v>2</v>
       </c>
       <c r="G136" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H136" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I136" t="s">
         <v>11</v>
@@ -5678,22 +5684,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C137" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D137" t="s">
+        <v>162</v>
+      </c>
+      <c r="E137" t="s">
         <v>163</v>
       </c>
-      <c r="E137" t="s">
-        <v>164</v>
-      </c>
       <c r="F137" t="s">
         <v>2</v>
       </c>
       <c r="G137" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="H137" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I137" t="s">
         <v>11</v>
@@ -5704,25 +5710,25 @@
         <v>18</v>
       </c>
       <c r="B138" t="s">
+        <v>165</v>
+      </c>
+      <c r="C138" t="s">
+        <v>375</v>
+      </c>
+      <c r="D138" t="s">
         <v>166</v>
       </c>
-      <c r="C138" t="s">
-        <v>380</v>
-      </c>
-      <c r="D138" t="s">
-        <v>167</v>
-      </c>
       <c r="E138" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F138" t="s">
         <v>2</v>
       </c>
       <c r="G138" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H138" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I138" t="s">
         <v>8</v>
@@ -5730,22 +5736,22 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C139" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D139" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E139" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F139" t="s">
         <v>2</v>
       </c>
       <c r="G139" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H139" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I139" t="s">
         <v>8</v>
@@ -5753,22 +5759,22 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C140" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D140" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="E140" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F140" t="s">
         <v>2</v>
       </c>
       <c r="G140" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H140" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I140" t="s">
         <v>11</v>
@@ -5776,22 +5782,22 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C141" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D141" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="E141" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F141" t="s">
         <v>2</v>
       </c>
       <c r="G141" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H141" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I141" t="s">
         <v>11</v>
@@ -5799,22 +5805,22 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C142" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="D142" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E142" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="F142" t="s">
         <v>2</v>
       </c>
       <c r="G142" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H142" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I142" t="s">
         <v>11</v>
@@ -5822,22 +5828,22 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C143" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D143" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E143" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="F143" t="s">
         <v>2</v>
       </c>
       <c r="G143" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H143" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I143" t="s">
         <v>11</v>
@@ -5845,22 +5851,22 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C144" t="s">
+        <v>168</v>
+      </c>
+      <c r="D144" t="s">
         <v>169</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
         <v>170</v>
       </c>
-      <c r="E144" t="s">
-        <v>171</v>
-      </c>
       <c r="F144" t="s">
         <v>2</v>
       </c>
       <c r="G144" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H144" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I144" t="s">
         <v>11</v>
@@ -5868,22 +5874,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C145" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D145" t="s">
+        <v>169</v>
+      </c>
+      <c r="E145" t="s">
         <v>170</v>
       </c>
-      <c r="E145" t="s">
-        <v>171</v>
-      </c>
       <c r="F145" t="s">
         <v>2</v>
       </c>
       <c r="G145" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H145" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I145" t="s">
         <v>11</v>
@@ -5894,25 +5900,25 @@
         <v>19</v>
       </c>
       <c r="B146" t="s">
+        <v>172</v>
+      </c>
+      <c r="C146" t="s">
         <v>173</v>
-      </c>
-      <c r="C146" t="s">
-        <v>174</v>
       </c>
       <c r="D146" t="s">
         <v>95</v>
       </c>
       <c r="E146" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F146" t="s">
         <v>2</v>
       </c>
       <c r="G146" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H146" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I146" t="s">
         <v>8</v>
@@ -5920,22 +5926,22 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C147" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D147" t="s">
         <v>95</v>
       </c>
       <c r="E147" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F147" t="s">
         <v>2</v>
       </c>
       <c r="G147" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H147" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I147" t="s">
         <v>8</v>
@@ -5943,22 +5949,22 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C148" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="D148" t="s">
         <v>56</v>
       </c>
       <c r="E148" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F148" t="s">
         <v>2</v>
       </c>
       <c r="G148" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H148" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I148" t="s">
         <v>11</v>
@@ -5966,22 +5972,22 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C149" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="D149" t="s">
         <v>56</v>
       </c>
       <c r="E149" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F149" t="s">
         <v>2</v>
       </c>
       <c r="G149" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H149" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I149" t="s">
         <v>11</v>
@@ -5989,22 +5995,22 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C150" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D150" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E150" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F150" t="s">
         <v>2</v>
       </c>
       <c r="G150" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H150" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I150" t="s">
         <v>11</v>
@@ -6012,22 +6018,22 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C151" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D151" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E151" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F151" t="s">
         <v>2</v>
       </c>
       <c r="G151" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H151" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I151" t="s">
         <v>11</v>
@@ -6035,22 +6041,22 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C152" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D152" t="s">
         <v>23</v>
       </c>
       <c r="E152" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F152" t="s">
         <v>2</v>
       </c>
       <c r="G152" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H152" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I152" t="s">
         <v>11</v>
@@ -6058,22 +6064,22 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C153" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D153" t="s">
         <v>23</v>
       </c>
       <c r="E153" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F153" t="s">
         <v>2</v>
       </c>
       <c r="G153" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H153" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I153" t="s">
         <v>11</v>
@@ -6084,25 +6090,25 @@
         <v>20</v>
       </c>
       <c r="B154" t="s">
+        <v>180</v>
+      </c>
+      <c r="C154" t="s">
         <v>181</v>
-      </c>
-      <c r="C154" t="s">
-        <v>182</v>
       </c>
       <c r="D154" t="s">
         <v>95</v>
       </c>
       <c r="E154" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F154" t="s">
         <v>2</v>
       </c>
       <c r="G154" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H154" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I154" t="s">
         <v>8</v>
@@ -6110,22 +6116,22 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C155" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D155" t="s">
         <v>95</v>
       </c>
       <c r="E155" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F155" t="s">
         <v>2</v>
       </c>
       <c r="G155" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H155" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I155" t="s">
         <v>8</v>
@@ -6133,22 +6139,22 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C156" t="s">
-        <v>185</v>
+        <v>669</v>
       </c>
       <c r="D156" t="s">
-        <v>95</v>
+        <v>657</v>
       </c>
       <c r="E156" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F156" t="s">
         <v>2</v>
       </c>
       <c r="G156" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H156" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I156" t="s">
         <v>11</v>
@@ -6156,22 +6162,22 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C157" t="s">
-        <v>187</v>
+        <v>670</v>
       </c>
       <c r="D157" t="s">
-        <v>95</v>
+        <v>657</v>
       </c>
       <c r="E157" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F157" t="s">
         <v>2</v>
       </c>
       <c r="G157" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H157" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I157" t="s">
         <v>11</v>
@@ -6179,22 +6185,22 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C158" t="s">
-        <v>188</v>
+        <v>671</v>
       </c>
       <c r="D158" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E158" t="s">
-        <v>183</v>
+        <v>673</v>
       </c>
       <c r="F158" t="s">
         <v>2</v>
       </c>
       <c r="G158" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H158" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I158" t="s">
         <v>11</v>
@@ -6202,22 +6208,22 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C159" t="s">
-        <v>190</v>
+        <v>672</v>
       </c>
       <c r="D159" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E159" t="s">
-        <v>183</v>
+        <v>673</v>
       </c>
       <c r="F159" t="s">
         <v>2</v>
       </c>
       <c r="G159" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H159" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I159" t="s">
         <v>11</v>
@@ -6225,22 +6231,22 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C160" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D160" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E160" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F160" t="s">
         <v>2</v>
       </c>
       <c r="G160" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H160" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I160" t="s">
         <v>11</v>
@@ -6248,22 +6254,22 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C161" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D161" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E161" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F161" t="s">
         <v>2</v>
       </c>
       <c r="G161" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H161" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I161" t="s">
         <v>11</v>
@@ -6274,25 +6280,25 @@
         <v>21</v>
       </c>
       <c r="B162" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C162" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D162" t="s">
         <v>47</v>
       </c>
       <c r="E162" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F162" t="s">
         <v>2</v>
       </c>
       <c r="G162" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H162" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I162" t="s">
         <v>8</v>
@@ -6300,22 +6306,22 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C163" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D163" t="s">
         <v>47</v>
       </c>
       <c r="E163" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F163" t="s">
         <v>2</v>
       </c>
       <c r="G163" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H163" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I163" t="s">
         <v>8</v>
@@ -6323,22 +6329,22 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C164" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D164" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="E164" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F164" t="s">
         <v>2</v>
       </c>
       <c r="G164" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H164" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I164" t="s">
         <v>11</v>
@@ -6346,22 +6352,22 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C165" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D165" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="E165" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F165" t="s">
         <v>2</v>
       </c>
       <c r="G165" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H165" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I165" t="s">
         <v>11</v>
@@ -6369,22 +6375,22 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C166" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D166" t="s">
         <v>51</v>
       </c>
       <c r="E166" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="F166" t="s">
         <v>2</v>
       </c>
       <c r="G166" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H166" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I166" t="s">
         <v>11</v>
@@ -6392,22 +6398,22 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C167" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D167" t="s">
         <v>51</v>
       </c>
       <c r="E167" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="F167" t="s">
         <v>2</v>
       </c>
       <c r="G167" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H167" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I167" t="s">
         <v>11</v>
@@ -6415,10 +6421,10 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C168" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D168" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E168" t="s">
         <v>63</v>
@@ -6427,10 +6433,10 @@
         <v>2</v>
       </c>
       <c r="G168" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H168" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I168" t="s">
         <v>11</v>
@@ -6438,10 +6444,10 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C169" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D169" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E169" t="s">
         <v>63</v>
@@ -6450,10 +6456,10 @@
         <v>2</v>
       </c>
       <c r="G169" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H169" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I169" t="s">
         <v>11</v>
@@ -6464,25 +6470,25 @@
         <v>22</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H170" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>8</v>
@@ -6491,22 +6497,22 @@
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B171" s="1"/>
       <c r="C171" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>137</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H171" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>8</v>
@@ -6515,22 +6521,22 @@
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B172" s="1"/>
       <c r="C172" s="1" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H172" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>11</v>
@@ -6539,22 +6545,22 @@
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B173" s="1"/>
       <c r="C173" s="1" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H173" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>11</v>
@@ -6563,22 +6569,22 @@
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B174" s="1"/>
       <c r="C174" s="1" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H174" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>11</v>
@@ -6587,22 +6593,22 @@
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B175" s="1"/>
       <c r="C175" s="1" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H175" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>11</v>
@@ -6611,22 +6617,22 @@
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B176" s="1"/>
       <c r="C176" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H176" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>11</v>
@@ -6635,22 +6641,22 @@
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B177" s="1"/>
       <c r="C177" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H177" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>11</v>
@@ -6661,25 +6667,25 @@
         <v>23</v>
       </c>
       <c r="B178" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C178" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D178" t="s">
         <v>127</v>
       </c>
       <c r="E178" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F178" t="s">
         <v>2</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H178" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I178" t="s">
         <v>8</v>
@@ -6687,22 +6693,22 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C179" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D179" t="s">
         <v>127</v>
       </c>
       <c r="E179" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F179" t="s">
         <v>2</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H179" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I179" t="s">
         <v>8</v>
@@ -6710,22 +6716,22 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C180" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="D180" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E180" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F180" t="s">
         <v>2</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H180" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I180" t="s">
         <v>11</v>
@@ -6733,22 +6739,22 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C181" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D181" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E181" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F181" t="s">
         <v>2</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H181" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I181" t="s">
         <v>11</v>
@@ -6756,22 +6762,22 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C182" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="D182" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E182" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F182" t="s">
         <v>2</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H182" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I182" t="s">
         <v>11</v>
@@ -6779,22 +6785,22 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C183" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D183" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E183" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F183" t="s">
         <v>2</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H183" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I183" t="s">
         <v>11</v>
@@ -6802,22 +6808,22 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C184" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D184" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E184" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F184" t="s">
         <v>2</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H184" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I184" t="s">
         <v>11</v>
@@ -6825,22 +6831,22 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C185" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D185" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E185" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F185" t="s">
         <v>2</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H185" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I185" t="s">
         <v>11</v>
@@ -6851,25 +6857,25 @@
         <v>24</v>
       </c>
       <c r="B186" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C186" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D186" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E186" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F186" t="s">
         <v>2</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H186" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I186" t="s">
         <v>8</v>
@@ -6877,22 +6883,22 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C187" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D187" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E187" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F187" t="s">
         <v>2</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H187" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I187" t="s">
         <v>8</v>
@@ -6900,22 +6906,22 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C188" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D188" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="E188" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F188" t="s">
         <v>2</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H188" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I188" t="s">
         <v>11</v>
@@ -6923,22 +6929,22 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C189" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="D189" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="E189" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F189" t="s">
         <v>2</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H189" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I189" t="s">
         <v>11</v>
@@ -6946,22 +6952,22 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C190" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="D190" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E190" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F190" t="s">
         <v>2</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H190" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I190" t="s">
         <v>11</v>
@@ -6969,22 +6975,22 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C191" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="D191" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E191" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F191" t="s">
         <v>2</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H191" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I191" t="s">
         <v>11</v>
@@ -6992,22 +6998,22 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C192" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D192" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E192" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F192" t="s">
         <v>2</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H192" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I192" t="s">
         <v>11</v>
@@ -7015,22 +7021,22 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C193" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D193" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E193" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F193" t="s">
         <v>2</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H193" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I193" t="s">
         <v>11</v>
@@ -7041,25 +7047,25 @@
         <v>25</v>
       </c>
       <c r="B194" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C194" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D194" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E194" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F194" t="s">
         <v>2</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H194" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I194" t="s">
         <v>8</v>
@@ -7067,22 +7073,22 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C195" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D195" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E195" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F195" t="s">
         <v>2</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H195" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I195" t="s">
         <v>8</v>
@@ -7090,22 +7096,22 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C196" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D196" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="E196" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F196" t="s">
         <v>2</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H196" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I196" t="s">
         <v>11</v>
@@ -7113,22 +7119,22 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C197" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D197" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="E197" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F197" t="s">
         <v>2</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H197" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I197" t="s">
         <v>11</v>
@@ -7136,22 +7142,22 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C198" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="D198" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E198" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="F198" t="s">
         <v>2</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H198" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I198" t="s">
         <v>11</v>
@@ -7159,22 +7165,22 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C199" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="D199" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E199" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="F199" t="s">
         <v>2</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H199" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I199" t="s">
         <v>11</v>
@@ -7182,22 +7188,22 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C200" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D200" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E200" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F200" t="s">
         <v>2</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H200" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I200" t="s">
         <v>11</v>
@@ -7205,22 +7211,22 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C201" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D201" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E201" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F201" t="s">
         <v>2</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H201" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I201" t="s">
         <v>11</v>
@@ -7231,25 +7237,25 @@
         <v>26</v>
       </c>
       <c r="B202" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C202" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D202" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E202" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F202" t="s">
         <v>2</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H202" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I202" t="s">
         <v>8</v>
@@ -7257,22 +7263,22 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C203" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D203" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E203" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F203" t="s">
         <v>2</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H203" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I203" t="s">
         <v>8</v>
@@ -7280,22 +7286,22 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C204" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D204" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="E204" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F204" t="s">
         <v>2</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H204" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I204" t="s">
         <v>11</v>
@@ -7303,22 +7309,22 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C205" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D205" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="E205" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F205" t="s">
         <v>2</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H205" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I205" t="s">
         <v>11</v>
@@ -7326,22 +7332,22 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C206" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="D206" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E206" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="F206" t="s">
         <v>2</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H206" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I206" t="s">
         <v>11</v>
@@ -7349,22 +7355,22 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C207" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D207" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E207" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="F207" t="s">
         <v>2</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H207" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I207" t="s">
         <v>11</v>
@@ -7372,22 +7378,22 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C208" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D208" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E208" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F208" t="s">
         <v>2</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H208" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I208" t="s">
         <v>11</v>
@@ -7395,22 +7401,22 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C209" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D209" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E209" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F209" t="s">
         <v>2</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H209" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I209" t="s">
         <v>11</v>
@@ -7421,13 +7427,13 @@
         <v>27</v>
       </c>
       <c r="B210" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C210" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D210" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E210" t="s">
         <v>70</v>
@@ -7436,10 +7442,10 @@
         <v>2</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H210" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I210" t="s">
         <v>8</v>
@@ -7447,10 +7453,10 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C211" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D211" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E211" t="s">
         <v>70</v>
@@ -7459,10 +7465,10 @@
         <v>2</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="H211" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I211" t="s">
         <v>8</v>
@@ -7470,22 +7476,22 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C212" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D212" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="E212" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F212" t="s">
         <v>2</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H212" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I212" t="s">
         <v>11</v>
@@ -7493,22 +7499,22 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C213" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D213" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="E213" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F213" t="s">
         <v>2</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="H213" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I213" t="s">
         <v>11</v>
@@ -7516,22 +7522,22 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C214" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D214" t="s">
         <v>67</v>
       </c>
       <c r="E214" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="F214" t="s">
         <v>2</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H214" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I214" t="s">
         <v>11</v>
@@ -7539,22 +7545,22 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C215" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D215" t="s">
         <v>67</v>
       </c>
       <c r="E215" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="F215" t="s">
         <v>2</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="H215" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I215" t="s">
         <v>11</v>
@@ -7562,22 +7568,22 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C216" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D216" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E216" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F216" t="s">
         <v>2</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H216" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I216" t="s">
         <v>11</v>
@@ -7585,22 +7591,22 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C217" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D217" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E217" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F217" t="s">
         <v>2</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="H217" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I217" t="s">
         <v>11</v>
@@ -7611,25 +7617,25 @@
         <v>28</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H218" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>8</v>
@@ -7638,22 +7644,22 @@
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B219" s="1"/>
       <c r="C219" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H219" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>8</v>
@@ -7662,22 +7668,22 @@
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B220" s="1"/>
       <c r="C220" s="1" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H220" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>11</v>
@@ -7686,22 +7692,22 @@
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B221" s="1"/>
       <c r="C221" s="1" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H221" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>11</v>
@@ -7710,22 +7716,22 @@
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B222" s="1"/>
       <c r="C222" s="1" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H222" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>11</v>
@@ -7734,22 +7740,22 @@
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B223" s="1"/>
       <c r="C223" s="1" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H223" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>11</v>
@@ -7758,22 +7764,22 @@
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B224" s="1"/>
       <c r="C224" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="H224" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>11</v>
@@ -7782,22 +7788,22 @@
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B225" s="1"/>
       <c r="C225" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H225" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>11</v>
@@ -7808,25 +7814,25 @@
         <v>29</v>
       </c>
       <c r="B226" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C226" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D226" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E226" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F226" t="s">
         <v>2</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H226" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I226" t="s">
         <v>8</v>
@@ -7834,22 +7840,22 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C227" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D227" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E227" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F227" t="s">
         <v>2</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="H227" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I227" t="s">
         <v>8</v>
@@ -7857,22 +7863,22 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C228" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="D228" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="E228" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F228" t="s">
         <v>2</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H228" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I228" t="s">
         <v>11</v>
@@ -7880,22 +7886,22 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C229" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D229" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="E229" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F229" t="s">
         <v>2</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="H229" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I229" t="s">
         <v>11</v>
@@ -7903,22 +7909,22 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C230" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="D230" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E230" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="F230" t="s">
         <v>2</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H230" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I230" t="s">
         <v>11</v>
@@ -7926,22 +7932,22 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C231" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D231" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E231" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="F231" t="s">
         <v>2</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="H231" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I231" t="s">
         <v>11</v>
@@ -7949,22 +7955,22 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C232" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D232" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E232" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F232" t="s">
         <v>2</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H232" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I232" t="s">
         <v>11</v>
@@ -7972,22 +7978,22 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C233" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D233" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E233" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F233" t="s">
         <v>2</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="H233" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I233" t="s">
         <v>11</v>
@@ -7998,25 +8004,25 @@
         <v>30</v>
       </c>
       <c r="B234" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C234" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D234" t="s">
         <v>47</v>
       </c>
       <c r="E234" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F234" t="s">
         <v>2</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H234" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I234" t="s">
         <v>8</v>
@@ -8024,22 +8030,22 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C235" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D235" t="s">
         <v>47</v>
       </c>
       <c r="E235" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F235" t="s">
         <v>2</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H235" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I235" t="s">
         <v>8</v>
@@ -8047,22 +8053,22 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C236" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D236" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="E236" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F236" t="s">
         <v>2</v>
       </c>
       <c r="G236" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H236" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I236" t="s">
         <v>11</v>
@@ -8070,22 +8076,22 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C237" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D237" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="E237" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F237" t="s">
         <v>2</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H237" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I237" t="s">
         <v>11</v>
@@ -8093,22 +8099,22 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C238" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="D238" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E238" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="F238" t="s">
         <v>2</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H238" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I238" t="s">
         <v>11</v>
@@ -8116,22 +8122,22 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C239" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D239" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E239" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="F239" t="s">
         <v>2</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H239" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I239" t="s">
         <v>11</v>
@@ -8139,22 +8145,22 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C240" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D240" t="s">
         <v>95</v>
       </c>
       <c r="E240" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F240" t="s">
         <v>2</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H240" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I240" t="s">
         <v>11</v>
@@ -8162,22 +8168,22 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C241" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D241" t="s">
         <v>95</v>
       </c>
       <c r="E241" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F241" t="s">
         <v>2</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H241" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I241" t="s">
         <v>11</v>
@@ -8188,25 +8194,25 @@
         <v>31</v>
       </c>
       <c r="B242" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C242" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="D242" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E242" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F242" t="s">
         <v>2</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H242" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I242" t="s">
         <v>8</v>
@@ -8214,22 +8220,22 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C243" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D243" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E243" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F243" t="s">
         <v>2</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H243" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I243" t="s">
         <v>8</v>
@@ -8237,22 +8243,22 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C244" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="D244" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="E244" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F244" t="s">
         <v>2</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H244" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I244" t="s">
         <v>11</v>
@@ -8260,22 +8266,22 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C245" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D245" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="E245" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F245" t="s">
         <v>2</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H245" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I245" t="s">
         <v>11</v>
@@ -8283,22 +8289,22 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C246" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D246" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E246" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="F246" t="s">
         <v>2</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H246" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I246" t="s">
         <v>11</v>
@@ -8306,22 +8312,22 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C247" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="D247" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E247" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="F247" t="s">
         <v>2</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H247" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I247" t="s">
         <v>11</v>
@@ -8329,22 +8335,22 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C248" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D248" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E248" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="F248" t="s">
         <v>2</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H248" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I248" t="s">
         <v>11</v>
@@ -8352,22 +8358,22 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C249" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D249" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E249" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="F249" t="s">
         <v>2</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="H249" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I249" t="s">
         <v>11</v>
@@ -8378,25 +8384,25 @@
         <v>32</v>
       </c>
       <c r="B250" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C250" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D250" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E250" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F250" t="s">
         <v>2</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H250" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I250" t="s">
         <v>8</v>
@@ -8404,22 +8410,22 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C251" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D251" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E251" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F251" t="s">
         <v>2</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="H251" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I251" t="s">
         <v>8</v>
@@ -8427,22 +8433,22 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C252" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="D252" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="E252" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F252" t="s">
         <v>2</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H252" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I252" t="s">
         <v>11</v>
@@ -8450,22 +8456,22 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C253" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="D253" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="E253" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F253" t="s">
         <v>2</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="H253" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I253" t="s">
         <v>11</v>
@@ -8473,22 +8479,22 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C254" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="D254" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E254" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="F254" t="s">
         <v>2</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H254" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I254" t="s">
         <v>11</v>
@@ -8496,22 +8502,22 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C255" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="D255" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E255" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="F255" t="s">
         <v>2</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="H255" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I255" t="s">
         <v>11</v>
@@ -8519,22 +8525,22 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C256" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D256" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E256" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F256" t="s">
         <v>2</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H256" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I256" t="s">
         <v>11</v>
@@ -8542,22 +8548,22 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C257" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D257" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E257" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F257" t="s">
         <v>2</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="H257" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I257" t="s">
         <v>11</v>
@@ -8568,25 +8574,25 @@
         <v>33</v>
       </c>
       <c r="B258" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C258" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D258" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E258" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F258" t="s">
         <v>2</v>
       </c>
       <c r="G258" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H258" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I258" t="s">
         <v>8</v>
@@ -8594,22 +8600,22 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C259" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D259" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E259" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F259" t="s">
         <v>2</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H259" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I259" t="s">
         <v>8</v>
@@ -8617,22 +8623,22 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C260" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="D260" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="E260" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F260" t="s">
         <v>2</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H260" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I260" t="s">
         <v>11</v>
@@ -8640,22 +8646,22 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C261" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D261" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="E261" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F261" t="s">
         <v>2</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H261" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I261" t="s">
         <v>11</v>
@@ -8663,22 +8669,22 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C262" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="D262" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E262" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="F262" t="s">
         <v>2</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H262" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I262" t="s">
         <v>11</v>
@@ -8686,22 +8692,22 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C263" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="D263" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E263" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="F263" t="s">
         <v>2</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H263" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I263" t="s">
         <v>11</v>
@@ -8709,22 +8715,22 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C264" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D264" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E264" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F264" t="s">
         <v>2</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H264" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I264" t="s">
         <v>11</v>
@@ -8732,22 +8738,22 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C265" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D265" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E265" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F265" t="s">
         <v>2</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H265" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I265" t="s">
         <v>11</v>
@@ -8758,25 +8764,25 @@
         <v>34</v>
       </c>
       <c r="B266" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C266" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D266" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E266" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F266" t="s">
         <v>2</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H266" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I266" t="s">
         <v>8</v>
@@ -8784,22 +8790,22 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C267" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D267" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E267" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F267" t="s">
         <v>2</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H267" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I267" t="s">
         <v>8</v>
@@ -8807,22 +8813,22 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C268" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="D268" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="E268" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F268" t="s">
         <v>2</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H268" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I268" t="s">
         <v>11</v>
@@ -8830,22 +8836,22 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C269" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D269" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="E269" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F269" t="s">
         <v>2</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H269" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I269" t="s">
         <v>11</v>
@@ -8853,22 +8859,22 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C270" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="D270" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E270" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="F270" t="s">
         <v>2</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H270" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I270" t="s">
         <v>11</v>
@@ -8876,22 +8882,22 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C271" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="D271" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E271" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="F271" t="s">
         <v>2</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H271" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I271" t="s">
         <v>11</v>
@@ -8899,22 +8905,22 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C272" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D272" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E272" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F272" t="s">
         <v>2</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H272" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I272" t="s">
         <v>11</v>
@@ -8922,22 +8928,22 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C273" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D273" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E273" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F273" t="s">
         <v>2</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H273" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I273" t="s">
         <v>11</v>
@@ -8948,25 +8954,25 @@
         <v>35</v>
       </c>
       <c r="B274" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C274" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D274" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E274" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F274" t="s">
         <v>2</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H274" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I274" t="s">
         <v>8</v>
@@ -8974,22 +8980,22 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C275" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D275" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E275" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F275" t="s">
         <v>2</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H275" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I275" t="s">
         <v>8</v>
@@ -8997,22 +9003,22 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C276" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="D276" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E276" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="F276" t="s">
         <v>2</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H276" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I276" t="s">
         <v>11</v>
@@ -9020,22 +9026,22 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C277" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D277" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E277" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="F277" t="s">
         <v>2</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H277" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I277" t="s">
         <v>11</v>
@@ -9043,22 +9049,22 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C278" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="D278" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E278" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="F278" t="s">
         <v>2</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H278" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I278" t="s">
         <v>11</v>
@@ -9066,22 +9072,22 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C279" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="D279" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E279" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="F279" t="s">
         <v>2</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H279" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I279" t="s">
         <v>11</v>
@@ -9089,10 +9095,10 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C280" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D280" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E280" t="s">
         <v>79</v>
@@ -9101,10 +9107,10 @@
         <v>2</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H280" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I280" t="s">
         <v>11</v>
@@ -9112,10 +9118,10 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C281" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D281" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E281" t="s">
         <v>79</v>
@@ -9124,10 +9130,10 @@
         <v>2</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H281" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I281" t="s">
         <v>11</v>
@@ -9138,25 +9144,25 @@
         <v>36</v>
       </c>
       <c r="B282" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C282" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D282" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E282" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F282" t="s">
         <v>2</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H282" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I282" t="s">
         <v>8</v>
@@ -9164,22 +9170,22 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C283" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D283" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E283" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F283" t="s">
         <v>2</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="H283" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I283" t="s">
         <v>8</v>
@@ -9187,22 +9193,22 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C284" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D284" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E284" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="F284" t="s">
         <v>2</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H284" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I284" t="s">
         <v>11</v>
@@ -9210,22 +9216,22 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C285" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D285" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E285" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="F285" t="s">
         <v>2</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="H285" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I285" t="s">
         <v>11</v>
@@ -9233,22 +9239,22 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C286" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="D286" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E286" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="F286" t="s">
         <v>2</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H286" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I286" t="s">
         <v>11</v>
@@ -9256,22 +9262,22 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C287" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="D287" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E287" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="F287" t="s">
         <v>2</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="H287" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I287" t="s">
         <v>11</v>
@@ -9279,7 +9285,7 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C288" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D288" t="s">
         <v>101</v>
@@ -9291,10 +9297,10 @@
         <v>2</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H288" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I288" t="s">
         <v>11</v>
@@ -9302,7 +9308,7 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C289" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D289" t="s">
         <v>101</v>
@@ -9314,10 +9320,10 @@
         <v>2</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="H289" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I289" t="s">
         <v>11</v>
@@ -9328,25 +9334,25 @@
         <v>37</v>
       </c>
       <c r="B290" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C290" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D290" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E290" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F290" t="s">
         <v>2</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H290" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I290" t="s">
         <v>8</v>
@@ -9354,22 +9360,22 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C291" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D291" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E291" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F291" t="s">
         <v>2</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H291" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I291" t="s">
         <v>8</v>
@@ -9377,22 +9383,22 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C292" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D292" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="E292" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F292" t="s">
         <v>2</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H292" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I292" t="s">
         <v>11</v>
@@ -9400,22 +9406,22 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C293" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="D293" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="E293" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F293" t="s">
         <v>2</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H293" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I293" t="s">
         <v>11</v>
@@ -9423,22 +9429,22 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C294" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="D294" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E294" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="F294" t="s">
         <v>2</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H294" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I294" t="s">
         <v>11</v>
@@ -9446,22 +9452,22 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C295" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="D295" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E295" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="F295" t="s">
         <v>2</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H295" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I295" t="s">
         <v>11</v>
@@ -9469,22 +9475,22 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C296" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D296" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E296" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F296" t="s">
         <v>2</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H296" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I296" t="s">
         <v>11</v>
@@ -9492,22 +9498,22 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C297" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D297" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E297" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F297" t="s">
         <v>2</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H297" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I297" t="s">
         <v>11</v>
@@ -9518,25 +9524,25 @@
         <v>38</v>
       </c>
       <c r="B298" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C298" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D298" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E298" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F298" t="s">
         <v>2</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H298" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I298" t="s">
         <v>8</v>
@@ -9544,22 +9550,22 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C299" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D299" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E299" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F299" t="s">
         <v>2</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="H299" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I299" t="s">
         <v>8</v>
@@ -9567,22 +9573,22 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C300" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="D300" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E300" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F300" t="s">
         <v>2</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H300" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I300" t="s">
         <v>11</v>
@@ -9590,22 +9596,22 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C301" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="D301" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E301" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F301" t="s">
         <v>2</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="H301" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I301" t="s">
         <v>11</v>
@@ -9613,22 +9619,22 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C302" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="D302" t="s">
         <v>51</v>
       </c>
       <c r="E302" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="F302" t="s">
         <v>2</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H302" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I302" t="s">
         <v>11</v>
@@ -9636,22 +9642,22 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C303" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="D303" t="s">
         <v>51</v>
       </c>
       <c r="E303" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="F303" t="s">
         <v>2</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="H303" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I303" t="s">
         <v>11</v>
@@ -9659,22 +9665,22 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C304" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D304" t="s">
         <v>87</v>
       </c>
       <c r="E304" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F304" t="s">
         <v>2</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H304" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I304" t="s">
         <v>11</v>
@@ -9682,22 +9688,22 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C305" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D305" t="s">
         <v>87</v>
       </c>
       <c r="E305" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F305" t="s">
         <v>2</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="H305" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I305" t="s">
         <v>11</v>
@@ -9708,25 +9714,25 @@
         <v>39</v>
       </c>
       <c r="B306" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C306" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D306" t="s">
         <v>40</v>
       </c>
       <c r="E306" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F306" t="s">
         <v>2</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H306" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I306" t="s">
         <v>8</v>
@@ -9734,22 +9740,22 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C307" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D307" t="s">
         <v>40</v>
       </c>
       <c r="E307" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F307" t="s">
         <v>2</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H307" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I307" t="s">
         <v>8</v>
@@ -9757,22 +9763,22 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C308" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D308" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="E308" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="F308" t="s">
         <v>2</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H308" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I308" t="s">
         <v>11</v>
@@ -9780,22 +9786,22 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C309" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="D309" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="E309" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="F309" t="s">
         <v>2</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H309" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I309" t="s">
         <v>11</v>
@@ -9803,22 +9809,22 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C310" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D310" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E310" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="F310" t="s">
         <v>2</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H310" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I310" t="s">
         <v>11</v>
@@ -9826,22 +9832,22 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C311" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="D311" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E311" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="F311" t="s">
         <v>2</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H311" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I311" t="s">
         <v>11</v>
@@ -9849,22 +9855,22 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C312" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D312" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E312" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F312" t="s">
         <v>2</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H312" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I312" t="s">
         <v>11</v>
@@ -9872,22 +9878,22 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C313" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D313" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E313" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F313" t="s">
         <v>2</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H313" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I313" t="s">
         <v>11</v>
@@ -9898,25 +9904,25 @@
         <v>40</v>
       </c>
       <c r="B314" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C314" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D314" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E314" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F314" t="s">
         <v>2</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H314" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I314" t="s">
         <v>8</v>
@@ -9924,22 +9930,22 @@
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C315" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D315" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E315" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F315" t="s">
         <v>2</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H315" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I315" t="s">
         <v>8</v>
@@ -9947,22 +9953,22 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C316" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D316" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E316" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="F316" t="s">
         <v>2</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H316" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I316" t="s">
         <v>11</v>
@@ -9970,22 +9976,22 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C317" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="D317" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E317" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="F317" t="s">
         <v>2</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H317" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I317" t="s">
         <v>11</v>
@@ -9993,22 +9999,22 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C318" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D318" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="E318" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="F318" t="s">
         <v>2</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H318" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I318" t="s">
         <v>11</v>
@@ -10016,22 +10022,22 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C319" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="D319" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="E319" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="F319" t="s">
         <v>2</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H319" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I319" t="s">
         <v>11</v>
@@ -10039,22 +10045,22 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C320" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D320" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E320" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F320" t="s">
         <v>2</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H320" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I320" t="s">
         <v>11</v>
@@ -10062,22 +10068,22 @@
     </row>
     <row r="321" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C321" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D321" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E321" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F321" t="s">
         <v>2</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H321" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I321" t="s">
         <v>11</v>
